--- a/data/daily/2026-09/2026-09-26.xlsx
+++ b/data/daily/2026-09/2026-09-26.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,60 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1425,102 +1425,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,79 +1578,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 제격 — 주는 사람과 받는 사람 모두 크게 만족하는 훌륭한 비타민 선물임</t>
+          <t>피로 회복 효과 — 섭취 후 피로 회복 및 활력 충전에 도움이 됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>우수한 피로회복 — 비싼 가격만큼 피로 회복과 건강 관리에 큰 도움을 줌</t>
+          <t>선물용 만족도 — 지인이나 동료에게 선물하거나 받기에 매우 유용하고 만족스러움</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 배송 처리가 빠르고 선물용 포장 상태도 좋음</t>
+          <t>간편한 섭취 — 병 단위로 되어 있어 먹기 편함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2659,17 +2659,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>편안한 목넘김 — 액상이 연하여 섭취 후 속쓰림이 없고 알약 크기가 작아 먹기 편함</t>
+          <t>부드러운 목넘김 — 액상이 연하고 주스 같아 속쓰림 없이 목넘김이 편함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 회복 효과 — 몸이 피곤하거나 컨디션이 저하되었을 때 기력을 돋우는 데 도움을 줌</t>
+          <t>알약 크기 만족 — 알약 크기가 작아 두 알을 한 번에 삼키기 수월함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>간편한 섭취 방법 — 하루 한 포씩 개별 구성되어 잊지 않고 챙겨 먹기 유용함</t>
+          <t>피로 회복 도움 — 섭취 후 피곤함 해소 및 컨디션 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2718,18 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 개선과 생기 — 섭취 후 활력이 넘치고 일상 속 피로감이 줄어드는 것을 체감함</t>
+          <t>활력 및 피로 개선 — 섭취 후 피곤함이 줄고 활력 있게 일하는 데 도움 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>합리적인 선물 — 쿠폰 할인 혜택으로 가격 부담 없이 명절 선물용으로 준비하기 좋음</t>
+          <t>명절 선물 적합 — 부담 없는 가격과 구성으로 명절이나 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>쇼핑백 불량 상태 — 선물용으로 동봉된 쇼핑백의 퀄리티가 불량하고 훼손된 채 배송됨</t>
+          <t>쇼핑백 불량 배송 — 선물용으로 동봉된 쇼핑백이 훼손되어 사용할 수 없는 상태로 배송됨</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2777,18 +2777,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>즉각적인 에너지 — 육아나 일상 피로로 지친 몸에 활력을 빠르게 보충해 줌</t>
+          <t>에너지 충전 효과 — 체력 소모가 크거나 피곤할 때 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>개별 포장의 편의 — 가방이나 책상에 넣어두고 언제든 꺼내 먹기 용이한 제형임</t>
+          <t>휴대 및 섭취 편의 — 개별 포장되어 있어 가방이나 책상에 두고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청 미반영 — 부재 시 관리실 위탁을 요청하였으나 문 앞에 두고 가 아쉬움</t>
+          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁을 요청했으나 문 앞에 두고 가 아쉬움 발생</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2832,26 +2832,26 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 회복과 맛 — 맛이 좋으며 피로가 빠르게 풀리는 기분을 느끼게 해 줌</t>
+          <t>브랜드 신뢰도 — 정관장 브랜드 제품이라 신뢰하고 안심하며 섭취함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 포장 상태가 우수하고 고급스러워 지인에게 선물하기에 아주 좋음</t>
+          <t>선물 패키지 만족 — 포장이 깔끔하고 예뻐 지인이나 부모님 선물용으로 좋음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>개별 포장의 장점 — 스틱으로 간편하게 개별 포장되어 바쁜 일상에서 섭취하기 편리함</t>
+          <t>맛과 피로 회복 — 맛이 좋으며 피로를 빠르게 푸는 데 도움이 됨</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>야간 복용 시 불면 — 저녁 시간대에 복용할 경우 활력 효과로 인해 잠들기 어려울 수 있음</t>
+          <t>저녁 섭취 시 각성 — 저녁 시간대에 복용할 경우 활력 증진으로 인해 잠들기 어려울 수 있음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2899,19 +2899,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>알찬 제품 구성 — 구성이 든든하고 넉넉한 분량이 들어 있어 장기 복용에 유용함</t>
+          <t>알찬 세트 구성 — 한 달치 용량에 쇼핑백까지 포함되어 선물 및 복용에 든든함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>신속한 배송 진행 — 연휴 기간임에도 불구하고 지연 없이 빠르게 상품이 도착함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>우수한 활력 효과 — 복용 후 에너지가 생기고 약효가 몸에 잘 받아 만족스러움</t>
-        </is>
-      </c>
+          <t>빠른 배송 만족 — 연휴 기간임에도 예상보다 배송이 빠르게 도착함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2958,27 +2954,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>활력 증진 및 체력 — 일이 많아 잠이 부족할 때 먹으면 덜 피곤하고 체력 관리에 도움을 줌</t>
+          <t>피로도 완화 효과 — 섭취 시 피로감이 줄어들어 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>섭취의 뛰어난 편의 — 사무실 등에서 하루에 한 번 간편하게 챙겨 먹기 유용함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>정성스러운 패키지 — 선물받았을 때 대접받는 느낌이 들 정도로 패키징 퀄리티가 우수함</t>
-        </is>
-      </c>
+          <t>간편한 복용 방식 — 액상과 캡슐이 함께 구성되어 사무실 등에서 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>위생 및 검수 불량 — 박스와 쇼핑백에 먼지와 이물질이 많이 묻은 채 배송되어 실망스러움</t>
+          <t>패키지 오염 불량 — 쇼핑백과 본품 상자에 먼지나 이물질이 묻은 상태로 배송됨</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>밀봉 스티커 훼손 — 입구 밀봉용 스티커가 반쯤 뜯겨 있고 손자국 흔적이 보여 불쾌함</t>
+          <t>밀봉 씰 훼손 — 밀봉 스티커가 반쯤 떼어져 있고 손자국이 남아 있어 검수 관리가 미흡함</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -3025,22 +3017,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>활력 넘치는 효능 — 매일 한 병씩 꾸준히 마시면 기력이 보충되고 확실히 힘이 남</t>
+          <t>높은 휴대성 — 개별 포장되어 있어 외출 시 간편하게 휴대 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>섭취의 뛰어난 편의 — 개별 포장 및 올인원 구성으로 번거로움 없이 비타민을 챙길 수 있음</t>
+          <t>맛있는 오렌지맛 — 오렌지 맛으로 비타민 특유의 거부감 없이 맛있게 복용함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 맛있는 오렌지 맛으로 구성되어 누구나 부담 없이 복용 가능함</t>
+          <t>활력 충전 만족 — 꾸준히 마시면 기운이 나고 피로 회복에 도움 됨</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>단독 복용의 불편함 — 물 없이 알약과 비타민제를 한꺼번에 삼키기에는 다소 뻑뻑함</t>
+          <t>알약 삼킴 어려움 — 비타민 정제가 다소 커서 물 없이 삼키기에는 불편함이 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3088,22 +3080,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>뛰어난 기력 증진 — 반짝이는 기분이 오래 유지되며 기존 제품보다 영양소가 풍부함</t>
+          <t>성별 맞춤 옵션 — 남녀 성별에 맞추어 영양소를 선택해 섭취할 수 있어 유용함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>옵션 선택의 장점 — 성별 맞춤(m/f)으로 옵션 선택이 가능하여 활용도가 우수함</t>
+          <t>지속적인 피로 개선 — 꾸준히 섭취 시 피로감이 덜하고 기운이 오래 유지됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>고품격 선물 포장 — 포장이 정성스럽고 깔끔하여 선물용으로 가치가 높음</t>
+          <t>고급스러운 포장 — 선물용으로 성의가 느껴지는 깔끔한 패키지 구성임</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>알약의 다소 큰 크기 — 알약 크기가 일반적인 제품보다 큰 편이라 삼킬 때 다소 힘듦</t>
+          <t>알약 크기 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3151,17 +3143,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>부담 없는 구미 형태 — 물 없이도 마이구미 젤리처럼 간편하고 즐겁게 씹어서 먹기 좋음</t>
+          <t>맛있는 젤리 제형 — 마이구미처럼 맛있고 상큼하여 간식처럼 즐기기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>훌륭한 맛과 식감 — 영양제 특유의 약 냄새가 전혀 없고 매우 맛이 좋음</t>
+          <t>물 없는 간편 섭취 — 구미 형태라 물 없이도 외출 전 손쉽게 복용 가능함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>귀여운 패키징 디자인 — 귤을 형상화한 귀여운 박스 및 캐릭터 굿즈가 포함되어 선물로 제격임</t>
+          <t>귀여운 선물 패키지 — 키캡 증정과 깔끔하고 귀여운 포장으로 가볍게 선물하기 적합함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3210,22 +3202,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 보자기 포장과 틴케이스, 핑크 박스가 돋보여 고급스러운 느낌을 줌</t>
+          <t>고급스러운 패키지 — 오간자 보자기 및 틴케이스 포장이 매우 예쁘고 정성스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않은 맛 — 콜라겐 특유의 비린 느낌이 없고 간식처럼 맛있게 복용 가능함</t>
+          <t>비리지 않은 맛 — 콜라겐 특유의 비린 맛이 없고 달콤상큼하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 낱개 앰플 형태로 제작되어 매일 한 병씩 가볍게 마시기 좋음</t>
+          <t>간편한 앰플 형태 — 개별 앰플 포장으로 간편하게 개봉하여 마실 수 있음</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>높은 가격대와 인상 — 효과는 만족스러우나 지속적인 가격 상승으로 구매 부담이 존재함</t>
+          <t>다소 높은 가격대 — 선물용으로는 좋으나 정가 기준 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3273,22 +3265,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>확실한 소화 개선 — 식사 후 복용 시 속이 편안하고 배변 활동에도 도움을 줌</t>
+          <t>소화 및 배변 도움 — 식후 섭취 시 속이 편안해지고 소화와 배변 활동에 도움 됨</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 고소하고 군고구마 같은 향으로 거부감 없이 맛있게 먹기 좋음</t>
+          <t>고소하고 편한 맛 — 곡물 맛으로 거부감 없이 고소하게 먹기 편함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>풍성한 혜택 구성 — 키위효소, 단백질바 등 풍부한 증정품과 빠른 배송 혜택을 제공함</t>
+          <t>풍성한 사은품 구성 — 단백질 바, 파인키위 효소 등 사은품 혜택이 만족스러움</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 크기 — 증정품인 고단백질바(단백질칩)의 용량이나 크기가 다소 협소함</t>
+          <t>증정품 용량 아쉬움 — 사은품으로 증정된 단백질 칩의 크기가 다소 작음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3297,7 +3289,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3305,58 +3297,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>900</v>
+        <v>56</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 타 쇼핑 채널보다 훨씬 합리적이고 저렴한 가격으로 구매함</t>
+          <t>부드러운 식감과 맛 — 퍽퍽하지 않고 매우 부드러우며 다양한 맛으로 질리지 않음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>푸짐하고 알찬 사은품 — 추가 포장용 증정 가방 및 과자 사은품 등이 풍부하여 만족스러움</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>속이 편안한 효과 — 자극 없이 더부룩함을 진정시켜 주고 위가 가뿐한 느낌을 줌</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>뛰어난 가성비 — 할인 적용 시 저렴한 가격에 다채로운 구성으로 구매 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>배송 중 해동 발생 — 냉동 상태가 유지되지 않고 제품이 전부 녹아서 배송됨</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3364,66 +3356,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>56</v>
+        <v>900</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>부드러운 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 부드러운 상태로 맛있게 먹을 수 있음</t>
+          <t>저렴한 구매 가격 — 용량 대비 합리적인 가격대로 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 소스, 스테이크, 주먹밥 등 여러 조합으로 질리지 않고 다이어트가 가능함</t>
+          <t>소화 편안함 — 식후 복용 시 더부룩하지 않고 속이 편안해지는 데 도움 됨</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 풍성한 수량 대비 가격이 대단히 저렴하여 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>배송 중 제품 해동 — 배송을 받았을 때 냉동 상태가 아니라 일부 내용물이 녹아 있어 아쉬움</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>특정 인기 종류 누락 — 가장 선호하는 파우치형 그릴 제품 라인이 제외되어 아쉬움을 남김</t>
-        </is>
-      </c>
+          <t>증정품 및 넉넉한 기한 — 파로칩 증정과 유통기한이 여유로워 보관 및 섭취에 용이함</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3431,62 +3415,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965673</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907090314_deefdfac70e6456194d7f4950eb47fcb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>759</v>
+        <v>215</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>고급스럽고 이쁜 외관 — 앰플 병 디자인과 패키지가 아기자기하고 고급스러워 선물용으로 안성맞춤임</t>
+          <t>비리지 않은 깔끔한 맛 — 특유의 비리고 텁텁한 맛 없이 초코우유처럼 달콤하고 깔끔함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 맛 — 거부감 있는 비린 향이 전혀 없으며 달달하고 새콤한 맛을 띰</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>단기 효과 미미함 — 복용 기간이 다소 짧아 단기간에는 확실한 외적 변화를 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>호불호가 갈리는 맛 — 개인의 미각에 따라 비타500과 감기약을 섞어둔 듯한 맛으로 체감될 수 있음</t>
-        </is>
-      </c>
+          <t>운동 후 단백질 보충 — 목넘김이 부드럽고 포만감이 있어 운동 후 간편 영양 보충에 적합함</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>슬림한 휴대성 — 패키지가 슬림하여 가방에 넣어 다니기 편리함</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3494,51 +3474,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907090314_deefdfac70e6456194d7f4950eb47fcb.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>215</v>
+        <v>759</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔함 — 단백질 음료 특유의 텁텁하고 비린 냄새가 없으며 부드럽게 넘어감</t>
+          <t>예쁜 선물 포장 — 고급스러운 앰플 병 디자인과 패키지가 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>훌륭한 맛과 제형 — 모카초콜릿, 딸기초코 등 인위적인 단맛 없이 우유처럼 자연스럽고 맛있음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>든든한 포만감 형성 — 운동 후 지쳤을 때 허기를 가볍게 채워주어 포만감을 채우기 좋음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>새콤한 비타민 맛 — 비타500과 유사한 새콤달콤한 맛으로 복용 거부감이 없음</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>단기 복용 시 미미한 효과 — 섭취 기간이 짧을 경우 가시적인 효과 체감이 어려움</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3584,22 +3564,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>더부룩함 없는 소화 — 식단 관리 중 소화에 문제가 생기거나 더부룩할 때 속을 다스리는 데 우수함</t>
+          <t>아이돌 굿즈 구성 — 포토카드 및 단백질 바 증정 구성으로 만족도가 높음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>맛있는 베리말차 맛 — 효소 특유의 퀴퀴함 없이 말차 맛이 은은하여 꾸준한 복용에 적합함</t>
+          <t>고소한 말차 맛 — 비리지 않고 고소한 베리말차 맛으로 섭취하기 좋음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>알찬 사은품 및 포카 — 좋아하는 연예인의 전용 굿즈와 단백질 바 등이 제공되어 가성비가 훌륭함</t>
+          <t>식후 속 편안함 — 식후 섭취 시 더부룩한 느낌이 줄어들고 속이 편안해짐</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>지연된 배송 기간 — 주문 후 출고 및 배송 도착까지 다소 오랜 시간이 소요됨</t>
+          <t>다소 느린 배송 — 주문 후 제품 수령까지 배송 기간이 다소 지연됨</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3647,22 +3627,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>뛰어난 아침 활력 — 이른 아침 공복에 섭취 시 에너지 충전에 도움을 주어 눈을 맑게 해 줌</t>
+          <t>모닝 활력 부스터 — 아침 공복에 마시면 눈이 뜨이고 활력이 충전되는 기분이 듦</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>거부감 없는 과일 맛 — 사과, 파인애플 등 상큼한 과일주스 풍미가 섞여 있어 생강을 맛있게 먹을 수 있음</t>
+          <t>상큼한 과일 블렌딩 — 생강의 매운맛을 사과와 레몬 등 과일 맛이 잡아주어 먹기 편함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>귀여운 편리한 보틀 — 미니 보틀 패키지가 귀여워 번거로운 일상 속에서도 손쉽게 챙겨 먹게 됨</t>
+          <t>귀여운 미니 보틀 — 병 디자인이 귀여워 섭취 시 기분 전환에 도움 됨</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>호불호 있는 생강 맛 — 생강의 매콤하고 알싸한 맛이 강하여 어린이나 일부 가족 구성원은 먹기 힘들어함</t>
+          <t>호불호 갈리는 생강 맛 — 생강 특유의 알싸한 맛으로 인해 아이나 일부 성인은 먹기 힘들어함</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3710,17 +3690,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>압도적인 활력 개선 — 초고함량 성분으로 지친 운동 일상에 지구력과 활력을 빠르게 메워줌</t>
+          <t>초고함량 아르기닌 — 1포당 6,200mg 고함량으로 빠른 활력 충전 및 운동에 도움 됨</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>휴대와 섭취의 편의 — 개별 스틱 액상 제형이라 외부 휴대나 물 없이 섭취하는 편리성이 우수함</t>
+          <t>간편한 섭취 및 휴대 — 개별 스틱 포장으로 하루 한 포 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>높은 함량과 신뢰성 — 6,200mg 고함량 설계와 믿을 수 있는 인물의 홍보로 제품을 더욱 신뢰하게 됨</t>
+          <t>쇼핑백 동봉 패키지 — 블랙과 레드의 고급스러운 패키지와 전용 쇼핑백으로 선물하기 좋음</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3738,51 +3718,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다채로운 체험팩 구성 — 음료, 쿠키, 쿠키바 등 여러 제형이 맛별로 구성되어 입문용으로 최고임</t>
+          <t>숙취 완화 효과 — 음주 전후 섭취 시 다음 날 숙취와 무거운 피로감이 덜함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>높은 디저트 퀄리티 — 부담스러운 프로틴 특유의 맛이 나지 않고 살찌는 디저트처럼 아주 만족스러움</t>
+          <t>간편한 스틱 액상형 — 물 없이 바로 짜 먹을 수 있어 모임 자리에서 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>뛰어난 선물성 패키지 — 포장 외관이 고급스럽고 규모가 커 보여 동호회 상품이나 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>고급스러운 선물 포장 — 깔끔하고 세련된 보라색 패키지로 지인 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>약재 맛 호불호 — 쌍화탕이나 한약 느낌의 쓴맛이 있어 쓴 맛에 민감한 경우 거부감이 들 수 있음</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4116,7 +4100,7 @@
         <v>796</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>779</v>
@@ -4142,70 +4126,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 제격 — 주는 사람과 받는 사람 모두 크게 만족하는 훌륭한 비타민 선물임
-우수한 피로회복 — 비싼 가격만큼 피로 회복과 건강 관리에 큰 도움을 줌
-신속한 배송 서비스 — 배송 처리가 빠르고 선물용 포장 상태도 좋음</t>
+          <t>피로 회복 효과 — 섭취 후 피로 회복 및 활력 충전에 도움이 됨
+선물용 만족도 — 지인이나 동료에게 선물하거나 받기에 매우 유용하고 만족스러움
+간편한 섭취 — 병 단위로 되어 있어 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>편안한 목넘김 — 액상이 연하여 섭취 후 속쓰림이 없고 알약 크기가 작아 먹기 편함
-피로 회복 효과 — 몸이 피곤하거나 컨디션이 저하되었을 때 기력을 돋우는 데 도움을 줌
-간편한 섭취 방법 — 하루 한 포씩 개별 구성되어 잊지 않고 챙겨 먹기 유용함</t>
+          <t>부드러운 목넘김 — 액상이 연하고 주스 같아 속쓰림 없이 목넘김이 편함
+알약 크기 만족 — 알약 크기가 작아 두 알을 한 번에 삼키기 수월함
+피로 회복 도움 — 섭취 후 피곤함 해소 및 컨디션 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선과 생기 — 섭취 후 활력이 넘치고 일상 속 피로감이 줄어드는 것을 체감함
-합리적인 선물 — 쿠폰 할인 혜택으로 가격 부담 없이 명절 선물용으로 준비하기 좋음</t>
+          <t>활력 및 피로 개선 — 섭취 후 피곤함이 줄고 활력 있게 일하는 데 도움 됨
+명절 선물 적합 — 부담 없는 가격과 구성으로 명절이나 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 에너지 — 육아나 일상 피로로 지친 몸에 활력을 빠르게 보충해 줌
-개별 포장의 편의 — 가방이나 책상에 넣어두고 언제든 꺼내 먹기 용이한 제형임</t>
+          <t>에너지 충전 효과 — 체력 소모가 크거나 피곤할 때 활력 증진에 도움 됨
+휴대 및 섭취 편의 — 개별 포장되어 있어 가방이나 책상에 두고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복과 맛 — 맛이 좋으며 피로가 빠르게 풀리는 기분을 느끼게 해 줌
-고급스러운 포장 — 포장 상태가 우수하고 고급스러워 지인에게 선물하기에 아주 좋음
-개별 포장의 장점 — 스틱으로 간편하게 개별 포장되어 바쁜 일상에서 섭취하기 편리함</t>
+          <t>브랜드 신뢰도 — 정관장 브랜드 제품이라 신뢰하고 안심하며 섭취함
+선물 패키지 만족 — 포장이 깔끔하고 예뻐 지인이나 부모님 선물용으로 좋음
+맛과 피로 회복 — 맛이 좋으며 피로를 빠르게 푸는 데 도움이 됨</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>알찬 제품 구성 — 구성이 든든하고 넉넉한 분량이 들어 있어 장기 복용에 유용함
-신속한 배송 진행 — 연휴 기간임에도 불구하고 지연 없이 빠르게 상품이 도착함
-우수한 활력 효과 — 복용 후 에너지가 생기고 약효가 몸에 잘 받아 만족스러움</t>
+          <t>알찬 세트 구성 — 한 달치 용량에 쇼핑백까지 포함되어 선물 및 복용에 든든함
+빠른 배송 만족 — 연휴 기간임에도 예상보다 배송이 빠르게 도착함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>활력 증진 및 체력 — 일이 많아 잠이 부족할 때 먹으면 덜 피곤하고 체력 관리에 도움을 줌
-섭취의 뛰어난 편의 — 사무실 등에서 하루에 한 번 간편하게 챙겨 먹기 유용함
-정성스러운 패키지 — 선물받았을 때 대접받는 느낌이 들 정도로 패키징 퀄리티가 우수함</t>
+          <t>피로도 완화 효과 — 섭취 시 피로감이 줄어들어 컨디션 관리에 도움 됨
+간편한 복용 방식 — 액상과 캡슐이 함께 구성되어 사무실 등에서 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>활력 넘치는 효능 — 매일 한 병씩 꾸준히 마시면 기력이 보충되고 확실히 힘이 남
-섭취의 뛰어난 편의 — 개별 포장 및 올인원 구성으로 번거로움 없이 비타민을 챙길 수 있음
-거부감 없는 맛 — 맛있는 오렌지 맛으로 구성되어 누구나 부담 없이 복용 가능함</t>
+          <t>높은 휴대성 — 개별 포장되어 있어 외출 시 간편하게 휴대 가능함
+맛있는 오렌지맛 — 오렌지 맛으로 비타민 특유의 거부감 없이 맛있게 복용함
+활력 충전 만족 — 꾸준히 마시면 기운이 나고 피로 회복에 도움 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 기력 증진 — 반짝이는 기분이 오래 유지되며 기존 제품보다 영양소가 풍부함
-옵션 선택의 장점 — 성별 맞춤(m/f)으로 옵션 선택이 가능하여 활용도가 우수함
-고품격 선물 포장 — 포장이 정성스럽고 깔끔하여 선물용으로 가치가 높음</t>
+          <t>성별 맞춤 옵션 — 남녀 성별에 맞추어 영양소를 선택해 섭취할 수 있어 유용함
+지속적인 피로 개선 — 꾸준히 섭취 시 피로감이 덜하고 기운이 오래 유지됨
+고급스러운 포장 — 선물용으로 성의가 느껴지는 깔끔한 패키지 구성임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 구미 형태 — 물 없이도 마이구미 젤리처럼 간편하고 즐겁게 씹어서 먹기 좋음
-훌륭한 맛과 식감 — 영양제 특유의 약 냄새가 전혀 없고 매우 맛이 좋음
-귀여운 패키징 디자인 — 귤을 형상화한 귀여운 박스 및 캐릭터 굿즈가 포함되어 선물로 제격임</t>
+          <t>맛있는 젤리 제형 — 마이구미처럼 맛있고 상큼하여 간식처럼 즐기기 좋음
+물 없는 간편 섭취 — 구미 형태라 물 없이도 외출 전 손쉽게 복용 가능함
+귀여운 선물 패키지 — 키캡 증정과 깔끔하고 귀여운 포장으로 가볍게 선물하기 적합함</t>
         </is>
       </c>
     </row>
@@ -4219,34 +4201,34 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 불량 상태 — 선물용으로 동봉된 쇼핑백의 퀄리티가 불량하고 훼손된 채 배송됨</t>
+          <t>쇼핑백 불량 배송 — 선물용으로 동봉된 쇼핑백이 훼손되어 사용할 수 없는 상태로 배송됨</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청 미반영 — 부재 시 관리실 위탁을 요청하였으나 문 앞에 두고 가 아쉬움</t>
+          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁을 요청했으나 문 앞에 두고 가 아쉬움 발생</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>야간 복용 시 불면 — 저녁 시간대에 복용할 경우 활력 효과로 인해 잠들기 어려울 수 있음</t>
+          <t>저녁 섭취 시 각성 — 저녁 시간대에 복용할 경우 활력 증진으로 인해 잠들기 어려울 수 있음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>위생 및 검수 불량 — 박스와 쇼핑백에 먼지와 이물질이 많이 묻은 채 배송되어 실망스러움
-밀봉 스티커 훼손 — 입구 밀봉용 스티커가 반쯤 뜯겨 있고 손자국 흔적이 보여 불쾌함</t>
+          <t>패키지 오염 불량 — 쇼핑백과 본품 상자에 먼지나 이물질이 묻은 상태로 배송됨
+밀봉 씰 훼손 — 밀봉 스티커가 반쯤 떼어져 있고 손자국이 남아 있어 검수 관리가 미흡함</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>단독 복용의 불편함 — 물 없이 알약과 비타민제를 한꺼번에 삼키기에는 다소 뻑뻑함</t>
+          <t>알약 삼킴 어려움 — 비타민 정제가 다소 커서 물 없이 삼키기에는 불편함이 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>알약의 다소 큰 크기 — 알약 크기가 일반적인 제품보다 큰 편이라 삼킬 때 다소 힘듦</t>
+          <t>알약 크기 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4457,22 +4439,22 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4514,24 +4496,24 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
@@ -4549,7 +4531,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -4571,24 +4553,24 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
@@ -4606,7 +4588,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -4660,16 +4642,16 @@
         <v>1679</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>56</v>
-      </c>
       <c r="G19" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>759</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>215</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>102</v>
@@ -4681,7 +4663,7 @@
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4692,75 +4674,74 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 보자기 포장과 틴케이스, 핑크 박스가 돋보여 고급스러운 느낌을 줌
-비리지 않은 맛 — 콜라겐 특유의 비린 느낌이 없고 간식처럼 맛있게 복용 가능함
-간편한 개별 포장 — 낱개 앰플 형태로 제작되어 매일 한 병씩 가볍게 마시기 좋음</t>
+          <t>고급스러운 패키지 — 오간자 보자기 및 틴케이스 포장이 매우 예쁘고 정성스러움
+비리지 않은 맛 — 콜라겐 특유의 비린 맛이 없고 달콤상큼하게 섭취 가능함
+간편한 앰플 형태 — 개별 앰플 포장으로 간편하게 개봉하여 마실 수 있음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>확실한 소화 개선 — 식사 후 복용 시 속이 편안하고 배변 활동에도 도움을 줌
-거부감 없는 맛 — 고소하고 군고구마 같은 향으로 거부감 없이 맛있게 먹기 좋음
-풍성한 혜택 구성 — 키위효소, 단백질바 등 풍부한 증정품과 빠른 배송 혜택을 제공함</t>
+          <t>소화 및 배변 도움 — 식후 섭취 시 속이 편안해지고 소화와 배변 활동에 도움 됨
+고소하고 편한 맛 — 곡물 맛으로 거부감 없이 고소하게 먹기 편함
+풍성한 사은품 구성 — 단백질 바, 파인키위 효소 등 사은품 혜택이 만족스러움</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 타 쇼핑 채널보다 훨씬 합리적이고 저렴한 가격으로 구매함
-푸짐하고 알찬 사은품 — 추가 포장용 증정 가방 및 과자 사은품 등이 풍부하여 만족스러움
-속이 편안한 효과 — 자극 없이 더부룩함을 진정시켜 주고 위가 가뿐한 느낌을 줌</t>
+          <t>부드러운 식감과 맛 — 퍽퍽하지 않고 매우 부드러우며 다양한 맛으로 질리지 않음
+뛰어난 가성비 — 할인 적용 시 저렴한 가격에 다채로운 구성으로 구매 가능함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 부드러운 상태로 맛있게 먹을 수 있음
-질리지 않는 다양한 맛 — 소스, 스테이크, 주먹밥 등 여러 조합으로 질리지 않고 다이어트가 가능함
-뛰어난 가성비 — 풍성한 수량 대비 가격이 대단히 저렴하여 가성비가 훌륭함</t>
+          <t>저렴한 구매 가격 — 용량 대비 합리적인 가격대로 부담 없이 섭취 가능함
+소화 편안함 — 식후 복용 시 더부룩하지 않고 속이 편안해지는 데 도움 됨
+증정품 및 넉넉한 기한 — 파로칩 증정과 유통기한이 여유로워 보관 및 섭취에 용이함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 이쁜 외관 — 앰플 병 디자인과 패키지가 아기자기하고 고급스러워 선물용으로 안성맞춤임
-상큼하고 맛있는 맛 — 거부감 있는 비린 향이 전혀 없으며 달달하고 새콤한 맛을 띰</t>
+          <t>비리지 않은 깔끔한 맛 — 특유의 비리고 텁텁한 맛 없이 초코우유처럼 달콤하고 깔끔함
+운동 후 단백질 보충 — 목넘김이 부드럽고 포만감이 있어 운동 후 간편 영양 보충에 적합함
+슬림한 휴대성 — 패키지가 슬림하여 가방에 넣어 다니기 편리함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔함 — 단백질 음료 특유의 텁텁하고 비린 냄새가 없으며 부드럽게 넘어감
-훌륭한 맛과 제형 — 모카초콜릿, 딸기초코 등 인위적인 단맛 없이 우유처럼 자연스럽고 맛있음
-든든한 포만감 형성 — 운동 후 지쳤을 때 허기를 가볍게 채워주어 포만감을 채우기 좋음</t>
+          <t>예쁜 선물 포장 — 고급스러운 앰플 병 디자인과 패키지가 선물용으로 훌륭함
+새콤한 비타민 맛 — 비타500과 유사한 새콤달콤한 맛으로 복용 거부감이 없음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 없는 소화 — 식단 관리 중 소화에 문제가 생기거나 더부룩할 때 속을 다스리는 데 우수함
-맛있는 베리말차 맛 — 효소 특유의 퀴퀴함 없이 말차 맛이 은은하여 꾸준한 복용에 적합함
-알찬 사은품 및 포카 — 좋아하는 연예인의 전용 굿즈와 단백질 바 등이 제공되어 가성비가 훌륭함</t>
+          <t>아이돌 굿즈 구성 — 포토카드 및 단백질 바 증정 구성으로 만족도가 높음
+고소한 말차 맛 — 비리지 않고 고소한 베리말차 맛으로 섭취하기 좋음
+식후 속 편안함 — 식후 섭취 시 더부룩한 느낌이 줄어들고 속이 편안해짐</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 아침 활력 — 이른 아침 공복에 섭취 시 에너지 충전에 도움을 주어 눈을 맑게 해 줌
-거부감 없는 과일 맛 — 사과, 파인애플 등 상큼한 과일주스 풍미가 섞여 있어 생강을 맛있게 먹을 수 있음
-귀여운 편리한 보틀 — 미니 보틀 패키지가 귀여워 번거로운 일상 속에서도 손쉽게 챙겨 먹게 됨</t>
+          <t>모닝 활력 부스터 — 아침 공복에 마시면 눈이 뜨이고 활력이 충전되는 기분이 듦
+상큼한 과일 블렌딩 — 생강의 매운맛을 사과와 레몬 등 과일 맛이 잡아주어 먹기 편함
+귀여운 미니 보틀 — 병 디자인이 귀여워 섭취 시 기분 전환에 도움 됨</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>압도적인 활력 개선 — 초고함량 성분으로 지친 운동 일상에 지구력과 활력을 빠르게 메워줌
-휴대와 섭취의 편의 — 개별 스틱 액상 제형이라 외부 휴대나 물 없이 섭취하는 편리성이 우수함
-높은 함량과 신뢰성 — 6,200mg 고함량 설계와 믿을 수 있는 인물의 홍보로 제품을 더욱 신뢰하게 됨</t>
+          <t>초고함량 아르기닌 — 1포당 6,200mg 고함량으로 빠른 활력 충전 및 운동에 도움 됨
+간편한 섭취 및 휴대 — 개별 스틱 포장으로 하루 한 포 간편하게 섭취 가능함
+쇼핑백 동봉 패키지 — 블랙과 레드의 고급스러운 패키지와 전용 쇼핑백으로 선물하기 좋음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 체험팩 구성 — 음료, 쿠키, 쿠키바 등 여러 제형이 맛별로 구성되어 입문용으로 최고임
-높은 디저트 퀄리티 — 부담스러운 프로틴 특유의 맛이 나지 않고 살찌는 디저트처럼 아주 만족스러움
-뛰어난 선물성 패키지 — 포장 외관이 고급스럽고 규모가 커 보여 동호회 상품이나 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>숙취 완화 효과 — 음주 전후 섭취 시 다음 날 숙취와 무거운 피로감이 덜함
+간편한 스틱 액상형 — 물 없이 바로 짜 먹을 수 있어 모임 자리에서 섭취하기 편리함
+고급스러운 선물 포장 — 깔끔하고 세련된 보라색 패키지로 지인 선물용으로 적합함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4768,40 +4749,42 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>높은 가격대와 인상 — 효과는 만족스러우나 지속적인 가격 상승으로 구매 부담이 존재함</t>
+          <t>다소 높은 가격대 — 선물용으로는 좋으나 정가 기준 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 크기 — 증정품인 고단백질바(단백질칩)의 용량이나 크기가 다소 협소함</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>배송 중 제품 해동 — 배송을 받았을 때 냉동 상태가 아니라 일부 내용물이 녹아 있어 아쉬움
-특정 인기 종류 누락 — 가장 선호하는 파우치형 그릴 제품 라인이 제외되어 아쉬움을 남김</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>단기 효과 미미함 — 복용 기간이 다소 짧아 단기간에는 확실한 외적 변화를 느끼기 어려움
-호불호가 갈리는 맛 — 개인의 미각에 따라 비타500과 감기약을 섞어둔 듯한 맛으로 체감될 수 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>증정품 용량 아쉬움 — 사은품으로 증정된 단백질 칩의 크기가 다소 작음</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>배송 중 해동 발생 — 냉동 상태가 유지되지 않고 제품이 전부 녹아서 배송됨</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 미미한 효과 — 섭취 기간이 짧을 경우 가시적인 효과 체감이 어려움</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>지연된 배송 기간 — 주문 후 출고 및 배송 도착까지 다소 오랜 시간이 소요됨</t>
+          <t>다소 느린 배송 — 주문 후 제품 수령까지 배송 기간이 다소 지연됨</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>호불호 있는 생강 맛 — 생강의 매콤하고 알싸한 맛이 강하여 어린이나 일부 가족 구성원은 먹기 힘들어함</t>
+          <t>호불호 갈리는 생강 맛 — 생강 특유의 알싸한 맛으로 인해 아이나 일부 성인은 먹기 힘들어함</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>약재 맛 호불호 — 쌍화탕이나 한약 느낌의 쓴맛이 있어 쓴 맛에 민감한 경우 거부감이 들 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4821,24 +4804,24 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>64,200원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>64,200원</t>
-        </is>
-      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>24,900원</t>
@@ -4856,7 +4839,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5029,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5054,43 +5037,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910777&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251229/5qFLremik89lsUa72Yqy610910777_00_005qFLremik89lsUa72Yqy.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1138</v>
+        <v>711</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>부드러운 목넘김 — 알약의 직경이 매우 작아 목넘길 때 이물감 없이 부드럽게 넘어감</t>
+          <t>혈당 관리 도움 — 식후 혈당 관리를 목적으로 간편하게 복용하기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>독보적인 가성비 혜택 — 다이소에서 부담 없이 저렴하게 구매해 장기간 챙겨 먹기 적합함</t>
+          <t>소용량 체험 적합 — 10일분의 소용량 구성이라 사전 테스트용으로 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5101,7 +5084,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5109,12 +5092,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5124,39 +5107,43 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580761&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250610/qUVshiLfS5KUSiQ9T3cu591580761_00_05qUVshiLfS5KUSiQ9T3cu.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>778</v>
+        <v>1021</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>합리적인 가성비 — 저렴한 가성비 가격대로 형성되어 장기 복용을 위한 유산균으로 재구매하기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>온가족이 쉬운 섭취 — 남녀노소 누구나 거부감 없이 손쉽게 털어먹을 수 있는 맛과 질감을 보임</t>
-        </is>
-      </c>
+          <t>우수한 가성비 — 다이소 유통 제품답게 가격 부담 없이 대량 구매가 가능함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>다이어트 체감 미미 — 복용 후 체중 감량이나 배변 활동에 뚜렷한 효과를 느끼지 못함</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>물 희석 시 단맛 — 물에 타 마실 때 인위적인 설탕물 맛이 나서 호불호가 갈림</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5164,7 +5151,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5174,41 +5161,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1198</v>
+        <v>4023</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>가성비 우수한 영양제 — 유명 제약사 브랜드 제품을 매우 만족스럽고 저렴한 가격에 복용함</t>
+          <t>극가성비 영양제 — 약국 대비 훨씬 저렴한 3천원대 가격으로 한 달분 섭취 가능함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>매일 꾸준한 복용 — 매일 한 알씩 챙겨 먹기 수월하여 온가족 일상 건강에 알맞음</t>
+          <t>작은 알약 크기 — 알약 크기가 작고 특이한 냄새가 없어 목넘김이 편함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>체감 효과 미미함 — 평소 가지고 있던 근육통 등에서 가시적인 통증 완화 효과를 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5223,62 +5206,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3667</v>
+        <v>90</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체지방 관리 지원 — 체지방 컷트에 도움을 주는 녹차 카테킨 성분이 있어 유용함</t>
+          <t>구강 상쾌함 유지 — 씹으면 캡슐이 톡 터지며 입안이 상쾌하고 시원해짐</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>운동 전 편리한 복용 — 복잡한 과정 없이 운동 가기 전 간편하게 하나씩 챙겨 먹기 좋음</t>
+          <t>간편한 에티켓 관리 — 식후나 양치가 어려운 상황에서 빠르게 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>다소 큰 알약 규격 — 기타 다이소 영양제에 비해 삼키는 알약의 부피가 커서 복용이 버거움</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>불명확한 단기 효능 — 일정 수준 복용 중이나 아직 구체적인 효과를 확신하기 어려움</t>
-        </is>
-      </c>
+          <t>캡슐 껍질 잔여감 — 씹은 후 남는 외피 껍질의 식감이 다소 애매함</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5286,12 +5265,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 피부건강＆면역 톡톡! 15일분</t>
+          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5301,43 +5280,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624079&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/0xJzkuIzlrFNcHO0q4lJ913624079_00_000xJzkuIzlrFNcHO0q4lJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>370</v>
+        <v>2343</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>뛰어난 맛의 만족도 — 거부감 없이 매우 맛있으며 피부와 장 건강 활성화에 좋을 것 같음</t>
+          <t>저렴한 유지 비용 — 가성비가 좋아 남성 건강 관리를 위해 꾸준히 재구매하기 용이함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>적절한 포장 규격 — 원하는 재질과 수량, 딱 필요한 사이즈로 제작되어 이용하기 편리함</t>
+          <t>예방 차원의 관리 — 부담 없는 가격대로 지속적인 사전 관리가 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>원산지에 대한 아쉬움 — 맛은 만족스러우나 첨가된 일부 성분의 원산지가 중국산인 점은 찝찝함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5345,12 +5320,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5360,51 +5335,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/8husYxWOSsou1qKUi5IE613602128_00_018husYxWOSsou1qKUi5IE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1073</v>
+        <v>1315</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있고 달콤한 젤리 — 일반적인 비타민 제품과 달리 맛이 훌륭하여 간식을 먹는 듯함</t>
+          <t>이온음료 같은 맛 — 포카리스웨트와 유사한 맛으로 거부감 없이 마시기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>아이들의 뛰어난 선호 — 알약을 기피하는 어린이들도 젤리 제형이라 거부하지 않고 주도적으로 먹음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>간편한 복용 방법 — 바쁜 아침 출근이나 등교할 때 입에 하나씩 넣어주기 수월함</t>
-        </is>
-      </c>
+          <t>짠 음식 섭취 후 붓기 완화 — 자극적이거나 짠 음식을 먹은 뒤 붓기를 가라앉히는 데 도움 됨</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>아쉬운 특유의 향 — 구미 특유의 냄새와 향이 약간의 기호 차이를 유발할 수 있음</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>단기 효과 체감 불가 — 한 달가량 짧은 섭취 기간으로는 몸에 나타나는 큰 피로 회복을 느끼기 어려움</t>
-        </is>
-      </c>
+          <t>다소 연한 농도 — 물에 희석했을 때 맛과 농도가 약간 밍밍하게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5412,12 +5379,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5427,28 +5394,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>962</v>
+        <v>363</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>젤리 타입의 섭취 편리 — 씹어 먹기 편한 구미 형태를 띠어 알약을 기피하는 분들도 쉽게 먹을 수 있음</t>
+          <t>진한 석류 맛 — 석류 특유의 새콤달콤하고 진한 맛이 느껴져 맛있게 섭취함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>즐거운 비타민 충전 — 맛있고 달달하게 비타민을 보충할 수 있어 매일 복용하는 과정이 흥미로움</t>
+          <t>저렴한 콜라겐 보충 — 가성비가 뛰어나 간편하게 일일 콜라겐을 챙기기 적합함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5459,7 +5426,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5467,12 +5434,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5482,38 +5449,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1325</v>
+        <v>892</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>저렴한 가성비 가격 — 콜라겐 영양제를 다이소에서 부담 없는 파격적인 가격에 구매함</t>
+          <t>달콤한 목 관리 — 달달한 맛으로 기관지 건강을 챙길 수 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>쉬운 목넘김과 제형 — 분말이나 가루가 아닌 알약이며 한 알 크기가 매우 작아 삼키기 좋음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>달콤하고 맛있는 맛 — 부담스러운 향 없이 섭취 시 달콤한 풍미가 느껴짐</t>
-        </is>
-      </c>
+          <t>저렴한 가격 만족 — 배도라지 스틱을 가성비 있게 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>단기 효과 체감 불가 — 지속 복용 중이나 영양제 특성상 외적으로 직접적인 개선을 느끼기엔 한계가 있음</t>
+          <t>맛에 대한 호불호 — 도라지 특유의 맛으로 인해 어린이나 초심자는 섭취가 다소 어려움</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -5530,12 +5493,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5545,28 +5508,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>202</v>
+        <v>1734</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>시원하게 녹는 공법 — 입에 닿는 순간 쓰지 않고 시원하며 부드럽게 사르르 녹아내림</t>
+          <t>수면 유도 도움 — 잠이 오지 않을 때 복용하면 편안한 입면에 도움 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>가성비와 편리함의 조화 — 저렴한 비용 대비 사용법이 대단히 편리하여 다방면으로 만족스러움</t>
+          <t>착한 가격대 — 다이소 매장에서 저렴하고 손쉽게 구매 가능함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5585,52 +5548,56 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/FWBWePRv27KbgtvBHof6613602132_00_01FWBWePRv27KbgtvBHof6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>740</v>
+        <v>2410</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>거부감 없는 젤리 — 하리보 젤리와 유사하여 씹어 먹는 재미가 있으며 영양제 거부감을 덜어줌</t>
+          <t>맛있는 파인애플맛 — 사탕처럼 달콤하고 깔끔해 간식 대용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>아이들에게 인기 — 아이들이 매일 자발적으로 챙겨 먹을 수 있을 만큼 친숙함</t>
+          <t>다리 붓기 완화 체감 — 오래 서 있는 날 복용 시 다음 날 다리 뻐근함과 붓기가 덜함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>호불호 갈리는 향 — 복용 전 겉으로 느껴지는 인위적인 향이 낯설거나 이상하게 다가올 수 있음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>복통 발생 — 섭취 후 배가 은은하게 아픈 복통 증상이 발생함</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>과도한 당분 함유 — 포도당 등 당류 함량이 높아 다이어트 시 섭취에 부담이 됨</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5744,42 +5711,42 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5801,52 +5768,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -5858,52 +5825,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 당케어</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 피부건강＆면역 톡톡! 15일분</t>
+          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
     </row>
@@ -5914,16 +5881,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5932,16 +5899,16 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5951,37 +5918,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1138</v>
+        <v>711</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>778</v>
+        <v>1021</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1198</v>
+        <v>4023</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3667</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>370</v>
+        <v>2343</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1073</v>
+        <v>1315</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>962</v>
+        <v>363</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1325</v>
+        <v>892</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>202</v>
+        <v>1734</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5989,64 +5956,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>부드러운 목넘김 — 알약의 직경이 매우 작아 목넘길 때 이물감 없이 부드럽게 넘어감
-독보적인 가성비 혜택 — 다이소에서 부담 없이 저렴하게 구매해 장기간 챙겨 먹기 적합함</t>
+          <t>혈당 관리 도움 — 식후 혈당 관리를 목적으로 간편하게 복용하기 좋음
+소용량 체험 적합 — 10일분의 소용량 구성이라 사전 테스트용으로 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>합리적인 가성비 — 저렴한 가성비 가격대로 형성되어 장기 복용을 위한 유산균으로 재구매하기 좋음
-온가족이 쉬운 섭취 — 남녀노소 누구나 거부감 없이 손쉽게 털어먹을 수 있는 맛과 질감을 보임</t>
+          <t>우수한 가성비 — 다이소 유통 제품답게 가격 부담 없이 대량 구매가 가능함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>가성비 우수한 영양제 — 유명 제약사 브랜드 제품을 매우 만족스럽고 저렴한 가격에 복용함
-매일 꾸준한 복용 — 매일 한 알씩 챙겨 먹기 수월하여 온가족 일상 건강에 알맞음</t>
+          <t>극가성비 영양제 — 약국 대비 훨씬 저렴한 3천원대 가격으로 한 달분 섭취 가능함
+작은 알약 크기 — 알약 크기가 작고 특이한 냄새가 없어 목넘김이 편함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체지방 관리 지원 — 체지방 컷트에 도움을 주는 녹차 카테킨 성분이 있어 유용함
-운동 전 편리한 복용 — 복잡한 과정 없이 운동 가기 전 간편하게 하나씩 챙겨 먹기 좋음</t>
+          <t>구강 상쾌함 유지 — 씹으면 캡슐이 톡 터지며 입안이 상쾌하고 시원해짐
+간편한 에티켓 관리 — 식후나 양치가 어려운 상황에서 빠르게 섭취하기 편리함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛의 만족도 — 거부감 없이 매우 맛있으며 피부와 장 건강 활성화에 좋을 것 같음
-적절한 포장 규격 — 원하는 재질과 수량, 딱 필요한 사이즈로 제작되어 이용하기 편리함</t>
+          <t>저렴한 유지 비용 — 가성비가 좋아 남성 건강 관리를 위해 꾸준히 재구매하기 용이함
+예방 차원의 관리 — 부담 없는 가격대로 지속적인 사전 관리가 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 달콤한 젤리 — 일반적인 비타민 제품과 달리 맛이 훌륭하여 간식을 먹는 듯함
-아이들의 뛰어난 선호 — 알약을 기피하는 어린이들도 젤리 제형이라 거부하지 않고 주도적으로 먹음
-간편한 복용 방법 — 바쁜 아침 출근이나 등교할 때 입에 하나씩 넣어주기 수월함</t>
+          <t>이온음료 같은 맛 — 포카리스웨트와 유사한 맛으로 거부감 없이 마시기 좋음
+짠 음식 섭취 후 붓기 완화 — 자극적이거나 짠 음식을 먹은 뒤 붓기를 가라앉히는 데 도움 됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>젤리 타입의 섭취 편리 — 씹어 먹기 편한 구미 형태를 띠어 알약을 기피하는 분들도 쉽게 먹을 수 있음
-즐거운 비타민 충전 — 맛있고 달달하게 비타민을 보충할 수 있어 매일 복용하는 과정이 흥미로움</t>
+          <t>진한 석류 맛 — 석류 특유의 새콤달콤하고 진한 맛이 느껴져 맛있게 섭취함
+저렴한 콜라겐 보충 — 가성비가 뛰어나 간편하게 일일 콜라겐을 챙기기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가성비 가격 — 콜라겐 영양제를 다이소에서 부담 없는 파격적인 가격에 구매함
-쉬운 목넘김과 제형 — 분말이나 가루가 아닌 알약이며 한 알 크기가 매우 작아 삼키기 좋음
-달콤하고 맛있는 맛 — 부담스러운 향 없이 섭취 시 달콤한 풍미가 느껴짐</t>
+          <t>달콤한 목 관리 — 달달한 맛으로 기관지 건강을 챙길 수 있음
+저렴한 가격 만족 — 배도라지 스틱을 가성비 있게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>시원하게 녹는 공법 — 입에 닿는 순간 쓰지 않고 시원하며 부드럽게 사르르 녹아내림
-가성비와 편리함의 조화 — 저렴한 비용 대비 사용법이 대단히 편리하여 다방면으로 만족스러움</t>
+          <t>수면 유도 도움 — 잠이 오지 않을 때 복용하면 편안한 입면에 도움 됨
+착한 가격대 — 다이소 매장에서 저렴하고 손쉽게 구매 가능함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 젤리 — 하리보 젤리와 유사하여 씹어 먹는 재미가 있으며 영양제 거부감을 덜어줌
-아이들에게 인기 — 아이들이 매일 자발적으로 챙겨 먹을 수 있을 만큼 친숙함</t>
+          <t>맛있는 파인애플맛 — 사탕처럼 달콤하고 깔끔해 간식 대용으로 먹기 좋음
+다리 붓기 완화 체감 — 오래 서 있는 날 복용 시 다음 날 다리 뻐근함과 붓기가 덜함</t>
         </is>
       </c>
     </row>
@@ -6057,39 +6021,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효과 미미함 — 평소 가지고 있던 근육통 등에서 가시적인 통증 완화 효과를 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>다이어트 체감 미미 — 복용 후 체중 감량이나 배변 활동에 뚜렷한 효과를 느끼지 못함
+물 희석 시 단맛 — 물에 타 마실 때 인위적인 설탕물 맛이 나서 호불호가 갈림</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 규격 — 기타 다이소 영양제에 비해 삼키는 알약의 부피가 커서 복용이 버거움
-불명확한 단기 효능 — 일정 수준 복용 중이나 아직 구체적인 효과를 확신하기 어려움</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>원산지에 대한 아쉬움 — 맛은 만족스러우나 첨가된 일부 성분의 원산지가 중국산인 점은 찝찝함</t>
-        </is>
-      </c>
+          <t>캡슐 껍질 잔여감 — 씹은 후 남는 외피 껍질의 식감이 다소 애매함</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 특유의 향 — 구미 특유의 냄새와 향이 약간의 기호 차이를 유발할 수 있음
-단기 효과 체감 불가 — 한 달가량 짧은 섭취 기간으로는 몸에 나타나는 큰 피로 회복을 느끼기 어려움</t>
+          <t>다소 연한 농도 — 물에 희석했을 때 맛과 농도가 약간 밍밍하게 느껴짐</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>단기 효과 체감 불가 — 지속 복용 중이나 영양제 특성상 외적으로 직접적인 개선을 느끼기엔 한계가 있음</t>
+          <t>맛에 대한 호불호 — 도라지 특유의 맛으로 인해 어린이나 초심자는 섭취가 다소 어려움</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 향 — 복용 전 겉으로 느껴지는 인위적인 향이 낯설거나 이상하게 다가올 수 있음</t>
+          <t>복통 발생 — 섭취 후 배가 은은하게 아픈 복통 증상이 발생함
+과도한 당분 함유 — 포도당 등 당류 함량이 높아 다이어트 시 섭취에 부담이 됨</t>
         </is>
       </c>
     </row>
@@ -6101,52 +6061,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6285,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6333,27 +6293,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6368,7 +6328,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6376,45 +6336,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>833</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>이너뷰티 이중 관리 — 탄수화물 커팅뿐만 아니라 안색 개선과 간 건강 활성화를 고루 도와줌</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>데일리 필수템 등극 — 효과가 우수하여 장기 복용을 목표로 매일 빼놓지 않는 필수 루틴으로 자리 잡음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -6423,7 +6371,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6431,27 +6379,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[먹는 앰플젤리] 푸드올로지 앰플젤리 7포 5종 택1(PDRN/글루타치온C/히알루론산/시카/NMN)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>12,600원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248686&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024868621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6466,7 +6414,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6474,50 +6422,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>516</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>이중 기능성 효과 보유 — 장 건강뿐 아니라 다이어트에 필수적인 체지방 관리까지 동시에 가능한 이중 제형임</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 풍미 — 부담스러운 맛이 아니라 상큼한 요거트 가루 맛이라 섭취 시 즐거움을 더함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>역대급 100원 특별 딜 — 기념 프로모션으로 수량을 대폭 추가 지급하는 선착순 100원 혜택이 훌륭함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6525,7 +6457,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6533,50 +6465,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>25409</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>초소형 캡슐 크기 — 170mg 단위의 매우 가볍고 작은 마이크로 캡슐이라 삼켰는지 모르게 쉽게 넘어감</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>질과 장 건강의 올인원 — 여성 이너케어를 위한 질 유산균과 일상 유산균을 한 캡슐로 다스릴 수 있음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>깜찍한 한정판 굿즈 — 포켓몬 에디션으로 출시되어 휴대폰에 붙이는 삐나 피카츄 카드 케이스 수령이 유용함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6584,7 +6500,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6592,45 +6508,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>딥트3일</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>16,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8245</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>소장 욕구 자극 굿즈 — 구매 욕구를 불러일으키는 키링 사은품이나 전속 배우 포토카드를 증정함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>건강한 아침 루틴 형성 — 매일 눈뜨자마자 따뜻한 물 한 잔과 함께 복용하여 건강한 습관을 갖기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6647,27 +6551,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>빌드</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6690,53 +6594,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>12712</v>
+        <v>26834</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>자극 없는 편안한 장 — 고보장 균수로 가스가 차거나 배가 아픈 증상 없이 깔끔하게 배변을 도와줌</t>
+          <t>단기 뱃살 정리 — 과식 후 복용 시 화장실을 잘 가게 되어 복부 팽만 완화에 도움 됨</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>귀여운 산리오 콜라보 — 태닝된 산리오 러기지택 굿즈가 사은품으로 구성되어 팬들의 마음을 사로잡음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>피부 면역 동시 관리 — 장이 편안해지면서 부가적으로 피부의 고른 안색과 면역 개선에도 기여함</t>
-        </is>
-      </c>
+          <t>일상 다이어트 관리 — 무리한 단식 없이 식단과 병행하며 체지방 관리를 돕는 보조제로 적합함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>알약의 커진 사이즈 — 기존에 복용하던 타제품들에 비해 캡슐 크기가 약간 두껍게 설정되어 있음</t>
+          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김에 부담이 될 수 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -6753,39 +6653,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>드시모네 키즈 스텝1 블루베리향 30포 2박스 (2개월분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>드시모네</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116,960원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000146546&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/B00000014654614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>51</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>5032</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>간식 같은 구미 제형 — 젤리 형태로 물 없이 씹어 먹을 수 있어 복용이 간편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>상큼한 맛과 활력 — 레몬라임 맛 등으로 맛이 상큼하여 피로할 때 기분 전환에 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>세일 시 가성비 우수 — 프로모션 기간에 합리적인 가격으로 쟁여두기 적합함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>양치 후 복용 번거로움 — 젤리 제형 특성상 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6800,37 +6716,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[총 1개월분] GNM 기억력 인지력 포스파티딜세린 징코 60캡슐 x 1박스 / PS 은행잎추출물 두뇌건강</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000214430&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/B00000021443002ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>18696</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>압도적인 가성비 — 커피 한 잔 수준의 매우 저렴한 가격대로 영양제를 골라 담을 수 있음</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>간편한 기초 영양 관리 — 휴대가 용이한 개별 포장 형태로 일상적인 활력 및 혈관 건강 관리에 유용함</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6947,32 +6871,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -7004,52 +6928,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>딥트3일</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>빌드</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>드시모네</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -7061,52 +6985,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[먹는 앰플젤리] 푸드올로지 앰플젤리 7포 5종 택1(PDRN/글루타치온C/히알루론산/시카/NMN)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>드시모네 키즈 스텝1 블루베리향 30포 2박스 (2개월분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[총 1개월분] GNM 기억력 인지력 포스파티딜세린 징코 60캡슐 x 1박스 / PS 은행잎추출물 두뇌건강</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
     </row>
@@ -7117,28 +7041,20 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -7148,28 +7064,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>833</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>516</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>25409</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>8245</v>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>12712</v>
+        <v>26834</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>51</v>
+        <v>5032</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>30</v>
+        <v>18696</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7179,43 +7087,31 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰티 이중 관리 — 탄수화물 커팅뿐만 아니라 안색 개선과 간 건강 활성화를 고루 도와줌
-데일리 필수템 등극 — 효과가 우수하여 장기 복용을 목표로 매일 빼놓지 않는 필수 루틴으로 자리 잡음</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>이중 기능성 효과 보유 — 장 건강뿐 아니라 다이어트에 필수적인 체지방 관리까지 동시에 가능한 이중 제형임
-상큼한 요거트 풍미 — 부담스러운 맛이 아니라 상큼한 요거트 가루 맛이라 섭취 시 즐거움을 더함
-역대급 100원 특별 딜 — 기념 프로모션으로 수량을 대폭 추가 지급하는 선착순 100원 혜택이 훌륭함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>초소형 캡슐 크기 — 170mg 단위의 매우 가볍고 작은 마이크로 캡슐이라 삼켰는지 모르게 쉽게 넘어감
-질과 장 건강의 올인원 — 여성 이너케어를 위한 질 유산균과 일상 유산균을 한 캡슐로 다스릴 수 있음
-깜찍한 한정판 굿즈 — 포켓몬 에디션으로 출시되어 휴대폰에 붙이는 삐나 피카츄 카드 케이스 수령이 유용함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>소장 욕구 자극 굿즈 — 구매 욕구를 불러일으키는 키링 사은품이나 전속 배우 포토카드를 증정함
-건강한 아침 루틴 형성 — 매일 눈뜨자마자 따뜻한 물 한 잔과 함께 복용하여 건강한 습관을 갖기 좋음</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>자극 없는 편안한 장 — 고보장 균수로 가스가 차거나 배가 아픈 증상 없이 깔끔하게 배변을 도와줌
-귀여운 산리오 콜라보 — 태닝된 산리오 러기지택 굿즈가 사은품으로 구성되어 팬들의 마음을 사로잡음
-피부 면역 동시 관리 — 장이 편안해지면서 부가적으로 피부의 고른 안색과 면역 개선에도 기여함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>단기 뱃살 정리 — 과식 후 복용 시 화장실을 잘 가게 되어 복부 팽만 완화에 도움 됨
+일상 다이어트 관리 — 무리한 단식 없이 식단과 병행하며 체지방 관리를 돕는 보조제로 적합함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>간식 같은 구미 제형 — 젤리 형태로 물 없이 씹어 먹을 수 있어 복용이 간편함
+상큼한 맛과 활력 — 레몬라임 맛 등으로 맛이 상큼하여 피로할 때 기분 전환에 좋음
+세일 시 가성비 우수 — 프로모션 기간에 합리적인 가격으로 쟁여두기 적합함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>압도적인 가성비 — 커피 한 잔 수준의 매우 저렴한 가격대로 영양제를 골라 담을 수 있음
+간편한 기초 영양 관리 — 휴대가 용이한 개별 포장 형태로 일상적인 활력 및 혈관 건강 관리에 유용함</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7232,10 +7128,14 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>알약의 커진 사이즈 — 기존에 복용하던 타제품들에 비해 캡슐 크기가 약간 두껍게 설정되어 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>다소 큰 알약 크기 — 정제의 크기가 다소 커서 삼킬 때 목넘김에 부담이 될 수 있음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>양치 후 복용 번거로움 — 젤리 제형 특성상 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7246,52 +7146,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>12,600원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>16,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>116,960원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7430,16 +7330,16 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7449,35 +7349,35 @@
         <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7496,16 +7396,16 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7518,38 +7418,38 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7565,28 +7465,6 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
